--- a/artfynd/A 55805-2020 artfynd.xlsx
+++ b/artfynd/A 55805-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55805-2020 artfynd.xlsx
+++ b/artfynd/A 55805-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,132 +932,6 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>89212921</v>
-      </c>
-      <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bockaskruv, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>543225.95710614</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6313149.152236868</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Uppvidinge</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Älghult</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2020-11-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2020-11-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Birgitta Warodell</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Birgitta Warodell</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
